--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,19 +512,19 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="21" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
@@ -851,10 +851,8 @@
           <t>Roshan Joshi</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9810627815</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9810627815</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -944,10 +942,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -958,7 +954,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1054,10 +1050,8 @@
           <t>Roshan Joshi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9810627815</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9810627815</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1147,10 +1141,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1161,30 +1153,237 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>1d 27m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 27m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:44 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi-6 Router ugrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370063</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:44:14 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 10:04:07 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:44:14 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.71839</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>hadi gaun marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>janak.adhikari211@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L5-8</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.33509</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 40m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1210,7 +1409,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1238,7 +1437,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1259,7 +1458,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1523,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1382,14 +1581,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1700,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1568,7 +1767,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1249,10 +1249,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843693628</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843693628</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1287,10 +1285,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.71839</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.71839</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1342,25 +1338,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L5-8</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33509</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33508999999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1378,6 +1378,109 @@
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1450,7 +1553,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1526,268 +1629,297 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1371454</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Roshan Joshi</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>1d 27m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 27m</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TKT1371454</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Roshan Joshi</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>1d 27m</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>1d 27m</t>
         </is>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1484,6 +1484,420 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371642</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Raj shahi</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Raj shahi</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9866252702</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:50:55 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841570819</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:47:52 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:02:10 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.72319</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Dallu Awasiya Vidhyalaya - School P852+V23, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>cazorlanwilshere@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>10:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.30066</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>1d 11m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:01 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:01:39 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.711797</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Stationery &amp; Gift Center, P863+MPJ, Purano Dhalko Marg, Kathmandu 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.304165</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1495,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1503,8 +1917,8 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1532,7 +1946,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1542,7 +1956,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1565,7 +1979,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 27m</t>
+          <t>1d 22m</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1991,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 27m</t>
+          <t>1d 23m</t>
         </is>
       </c>
     </row>
@@ -1618,14 +2032,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1690,14 +2104,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1925,6 +2339,73 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371642</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Raj shahi</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:50:55 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:47:52 AM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:02:10 PM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>1d 11m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1551,10 +1551,8 @@
           <t>Raj shahi</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9866252702</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9866252702</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1589,10 +1587,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.72319</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.72319</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1648,25 +1644,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.30066</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.30065999999999</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1762,10 +1754,8 @@
           <t>Ramita Pujari</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9818579073</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9818579073</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1800,10 +1790,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.711797</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.711797</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1851,48 +1839,255 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.304165</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.304165</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>1d 34m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>1d 34m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi-6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370690</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Preju Khanal</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Preju Khanal</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9863593710</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:14:40 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860561433</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:14:40 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:12:32 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.73229</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Banasthali Siddhartha Tole , Kharibot, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>khnl.preju16@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>16:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Parvati Baduwal</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB432</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.29094</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1909,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1946,7 +2141,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1956,7 +2151,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1967,7 +2162,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1979,7 +2174,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 22m</t>
+          <t>1d 5h 31m</t>
         </is>
       </c>
     </row>
@@ -1991,7 +2186,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23m</t>
+          <t>1d 5h 31m</t>
         </is>
       </c>
     </row>
@@ -2032,14 +2227,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2104,14 +2299,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2372,14 +2567,14 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 11:50:55 AM</t>
@@ -2403,6 +2598,73 @@
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>1d 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1370690</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Preju Khanal</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:14:40 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 03:14:40 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:12:32 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,14 +511,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1949,10 +1949,8 @@
           <t>Preju Khanal</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9863593710</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9863593710</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1987,10 +1985,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.73229</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.73229</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2046,50 +2042,261 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB432</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.29094</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.29094000000001</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 57m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 57m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 57m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>stb faulty</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372115</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9849149003</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:10:35 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9849149003</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:00:54 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:27:38 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.7238</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Basnettar Tarakeshwar 44600 - Kathmandu Metropolitan, Bagmati, Kathmandu, Nepal, Nepal, Kathmandu, N</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>herosudeep7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>03:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.30359</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>17h 17m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>17h 26m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2104,13 +2311,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -2141,7 +2348,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2151,7 +2358,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2162,7 +2369,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2381,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 5h 31m</t>
+          <t>1d 3h 4m</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2393,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 31m</t>
+          <t>1d 3h 6m</t>
         </is>
       </c>
     </row>
@@ -2239,310 +2446,217 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1371642</t>
+          <t>TKT1371454</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Raj shahi</t>
+          <t>Roshan Joshi</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2557,12 +2671,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2572,99 +2686,300 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 11:50:55 AM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 11:47:52 AM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:02:10 PM</t>
+          <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>1d 11m</t>
+          <t>1d 27m</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TKT1371454</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Roshan Joshi</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:46:24 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 09:46:24 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:14:03 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>1d 27m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>1d 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371642</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Raj shahi</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:50:55 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:47:52 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:02:10 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>1d 11m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1370690</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Preju Khanal</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>16 Oct 2026 12:12:32 PM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>1d 20h 57m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>1d 20h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372115</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:10:35 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:00:54 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:27:38 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>17h 17m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>17h 26m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2152,10 +2152,8 @@
           <t>Sudip Danai</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9849149003</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9849149003</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2190,10 +2188,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.7238</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.7238</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2231,10 +2227,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2253,25 +2247,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.30359</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.30359</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2320,7 +2310,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2949,7 +2939,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,10 +512,10 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
     <col width="28" customWidth="1" min="33" max="33"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2290,6 +2290,428 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6g router</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372450</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841321261</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841321261</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:02 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:41:11 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.757137</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Dharmasthali 27.757099,85.291095 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>devkotarmd777@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>02:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.29122</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>3h 12m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6g router</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372450</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841321261</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841321261</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:02 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:41:11 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.757137</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Dharmasthali 27.757099,85.291095 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>devkotarmd777@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>02:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.29122</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>3h 12m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2301,7 +2723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2732,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2338,7 +2760,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2348,7 +2770,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2359,7 +2781,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2793,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 4m</t>
+          <t>20h 15m</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2805,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 6m</t>
+          <t>20h 17m</t>
         </is>
       </c>
     </row>
@@ -2424,14 +2846,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2514,14 +2936,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2973,6 +3395,140 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372450</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:02 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:41:11 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>3h 12m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372450</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Rammani Devkota</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:28:02 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:41:11 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>3h 12m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2357,10 +2357,8 @@
           <t>Rammani Devkota</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841321261</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841321261</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2395,10 +2393,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.757137</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.757137</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2454,25 +2450,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.29122</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.29122</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2568,10 +2560,8 @@
           <t>Rammani Devkota</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841321261</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841321261</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2606,10 +2596,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.757137</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.757137</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2665,25 +2653,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.29122</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.29122</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2732,7 +2716,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3428,7 +3412,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -3495,7 +3479,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2696,6 +2696,217 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9803605258</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9803605258</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.71469</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Next to Swoyambhu Area Post Office,Swoyambhu,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>Akc68225@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>03:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.28644</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2707,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2716,7 +2927,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2744,7 +2955,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2754,7 +2965,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2765,7 +2976,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2988,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 15m</t>
+          <t>18h 12m</t>
         </is>
       </c>
     </row>
@@ -2789,7 +3000,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 17m</t>
+          <t>18h 14m</t>
         </is>
       </c>
     </row>
@@ -2830,14 +3041,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2920,14 +3131,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -3513,6 +3724,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2763,10 +2763,8 @@
           <t>Abhaya Kc</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9803605258</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9803605258</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2801,10 +2799,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.71469</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.71469</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2860,48 +2856,565 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.28644</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.28644</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 1:32 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9803605258</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9803605258</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.71469</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Next to Swoyambhu Area Post Office,Swoyambhu,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>Akc68225@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>03:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.28644</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
         <is>
           <t>3h 53m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
+      <c r="AT14" s="3" t="inlineStr">
         <is>
           <t>3h 53m</t>
         </is>
       </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AU14" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
+      <c r="AV14" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371924</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Pujari</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Pujari</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9803557654</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:48:18 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9803557654</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:48:18 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:33:51 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.739038</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near Ganesh Mandir gongabu Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>07:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L41-1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.314078</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>21h 45m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>21h 45m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2918,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2955,7 +3468,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2965,7 +3478,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2976,7 +3489,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3501,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>18h 12m</t>
+          <t>17h 7m</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3513,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 14m</t>
+          <t>17h 9m</t>
         </is>
       </c>
     </row>
@@ -3041,14 +3554,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -3131,14 +3644,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -3757,37 +4270,171 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 01:32:15 PM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>3h 53m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371924</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Pawan Pujari</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:48:18 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:48:18 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:33:51 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>21h 45m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>21h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3069,10 +3069,8 @@
           <t>Abhaya Kc</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9803605258</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9803605258</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3107,10 +3105,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.71469</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.71469</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3166,25 +3162,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.28644</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.28644</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3280,10 +3272,8 @@
           <t>Pawan Pujari</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9803557654</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9803557654</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3318,10 +3308,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.739038</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.739038</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3373,25 +3361,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>L41-1</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.314078</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31407799999999</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3440,7 +3424,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4337,7 +4321,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -4404,7 +4388,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="36" customWidth="1" min="32" max="32"/>
     <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3404,6 +3404,1252 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:08 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372400</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Samir Duwadi</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Samir Duwadi</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9869421251</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:45:59 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9869421251</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:45:59 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:36 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.703253</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu royal decor and parquet house,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>samirnilkanthaduwadi947@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>04:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.272708</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1369621</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 07:58:45 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 07:58:45 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:14:54 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 16m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 16m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:09 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372633</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Sea Design Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Sea Design Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9801015263</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:09:02 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9801015263</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:00:37 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:09:02 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.68196</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Universal Engineering &amp; Science College /, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>sea_design@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>03:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.32759</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>3h 8m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:08 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372117</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851026565</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:26 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851026565</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:02:29 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:26 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Bikash Bank Limited Jyoti Bikash Bank Limited - Bank 31 Pashupati Sadak Kathmandu 44600, Bagma</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9808233586@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>05:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>19h 5m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi-6 Router ugrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1370063</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:07:25 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9843693628</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 10:04:07 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:07:25 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.71839</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>hadi gaun marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>janak.adhikari211@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>00:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L5-8</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.33509</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 3m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372009</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Kc</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Kc</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9860480690</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:06:46 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9617724003C</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 04:47:00 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:06:46 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.71925</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Boudhanath Sadak, Siddhartha Cinema Private Limited, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>bikashkc25@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L26-1</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.3607</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>21h 19m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3415,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3424,7 +4670,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3452,7 +4698,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -3462,7 +4708,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3473,7 +4719,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3485,7 +4731,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 7m</t>
+          <t>11h 46m</t>
         </is>
       </c>
     </row>
@@ -3497,7 +4743,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 9m</t>
+          <t>18h 10m</t>
         </is>
       </c>
     </row>
@@ -3538,14 +4784,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -3568,333 +4814,240 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>81.8%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1371642</t>
+          <t>TKT1371454</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Raj shahi</t>
+          <t>Roshan Joshi</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3909,12 +5062,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3924,44 +5077,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 11:50:55 AM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 11:47:52 AM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:02:10 PM</t>
+          <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1d 11m</t>
+          <t>1d 27m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1370690</t>
+          <t>TKT1371454</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Preju Khanal</t>
+          <t>Roshan Joshi</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3991,64 +5144,64 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>14 Oct 2026 03:14:40 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>14 Oct 2026 03:14:40 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:12:32 PM</t>
+          <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 57m</t>
+          <t>1d 27m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 57m</t>
+          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1372115</t>
+          <t>TKT1371642</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sudip Danai</t>
+          <t>Raj shahi</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4058,44 +5211,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 07:10:35 PM</t>
+          <t>15 Oct 2026 11:50:55 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 07:00:54 PM</t>
+          <t>15 Oct 2026 11:47:52 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:27:38 PM</t>
+          <t>16 Oct 2026 12:02:10 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>17h 17m</t>
+          <t>1d 11m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>17h 26m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1372450</t>
+          <t>TKT1370690</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Rammani Devkota</t>
+          <t>Preju Khanal</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4125,54 +5278,54 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:48 AM</t>
+          <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:02 AM</t>
+          <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:41:11 PM</t>
+          <t>16 Oct 2026 12:12:32 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>3h 12m</t>
+          <t>1d 20h 57m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>3h 13m</t>
+          <t>1d 20h 57m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1372450</t>
+          <t>TKT1372115</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Rammani Devkota</t>
+          <t>Sudip Danai</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4192,44 +5345,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:48 AM</t>
+          <t>15 Oct 2026 07:10:35 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:02 AM</t>
+          <t>15 Oct 2026 07:00:54 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:41:11 PM</t>
+          <t>16 Oct 2026 12:27:38 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3h 12m</t>
+          <t>17h 17m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>3h 13m</t>
+          <t>17h 26m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1372464</t>
+          <t>TKT1372450</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Abhaya Kc</t>
+          <t>Rammani Devkota</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4259,44 +5412,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:48 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:02 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:32:15 PM</t>
+          <t>16 Oct 2026 12:41:11 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 12m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 13m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1372464</t>
+          <t>TKT1372450</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Abhaya Kc</t>
+          <t>Rammani Devkota</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4326,99 +5479,568 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:48 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:02 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:32:15 PM</t>
+          <t>16 Oct 2026 12:41:11 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 12m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 13m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372464</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Abhaya Kc</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 09:38:30 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:32:15 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1371924</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Pawan Pujari</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>15 Oct 2026 03:48:18 PM</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>15 Oct 2026 03:48:18 PM</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>16 Oct 2026 01:33:51 PM</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>21h 45m</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>21h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372400</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Samir Duwadi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:45:59 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:45:59 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:36 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372633</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Sea Design Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:09:02 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:00:37 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:09:02 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>3h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372117</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Bibek shrestha</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:26 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:02:29 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:08:26 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>19h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1370063</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:07:25 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>14 Oct 2026 10:04:07 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:07:25 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2d 4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372009</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Kc</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:06:46 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 04:47:00 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:06:46 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>21h 19m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3471,10 +3471,8 @@
           <t>Samir Duwadi</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9869421251</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9869421251</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3509,10 +3507,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.703253</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.703253</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3568,25 +3564,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.272708</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.27270799999999</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3672,20 +3664,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3771,10 +3757,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3785,7 +3769,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3881,10 +3865,8 @@
           <t>Sea Design Pvt Ltd</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9801015263</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9801015263</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3919,10 +3901,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.68196</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.68196</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3978,25 +3958,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,16</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.32759</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.32759</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4092,10 +4068,8 @@
           <t>Bibek shrestha</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851026565</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851026565</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4185,10 +4159,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4199,7 +4171,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4295,10 +4267,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9843693628</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9843693628</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4333,10 +4303,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.71839</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.71839</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4392,25 +4360,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L5-8</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.33509</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.33508999999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4506,10 +4470,8 @@
           <t>Bikash Kc</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9860480690</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9860480690</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4544,10 +4506,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.71925</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.71925</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4603,48 +4563,450 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L26-1</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.3607</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.36069999999999</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>21h 19m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>21h 19m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:20 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841266733</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841266733</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Dallu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>kclalita31@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB436E</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:19 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841266733</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841266733</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Dallu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>kclalita31@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>11:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB436E</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4661,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4698,7 +5060,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4708,7 +5070,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4719,7 +5081,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -4731,7 +5093,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 46m</t>
+          <t>13h 21m</t>
         </is>
       </c>
     </row>
@@ -4743,7 +5105,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 10m</t>
+          <t>18h 59m</t>
         </is>
       </c>
     </row>
@@ -4784,14 +5146,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -4892,14 +5254,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -5742,7 +6104,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -5809,7 +6171,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -5876,7 +6238,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -5943,7 +6305,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -6010,14 +6372,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 02:06:46 PM</t>
@@ -6041,6 +6403,140 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>21h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4673,10 +4673,8 @@
           <t>Sanjeev Shahi</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841266733</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841266733</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4766,10 +4764,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4780,7 +4776,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4876,10 +4872,8 @@
           <t>Sanjeev Shahi</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841266733</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841266733</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4969,10 +4963,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4983,30 +4975,639 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 12m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 12m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:37 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371906</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9707987556</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>CHB9707987556</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:37:15 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Nardevi Ayurvedic Hospital - Hospital P854+34V Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9707987556@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB298</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:36 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371906</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9707987556</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>CHB9707987556</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:37:15 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Nardevi Ayurvedic Hospital - Hospital P854+34V Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9707987556@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB298</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:33 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:33:11 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.711797</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Stationery &amp; Gift Center, P863+MPJ, Purano Dhalko Marg, Kathmandu 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.304165</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 5m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 5m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5023,7 +5624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5060,7 +5661,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -5070,7 +5671,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5081,7 +5682,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5694,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13h 21m</t>
+          <t>14h 23m</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5706,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 59m</t>
+          <t>19h 25m</t>
         </is>
       </c>
     </row>
@@ -5146,14 +5747,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -5254,14 +5855,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -6439,7 +7040,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -6506,14 +7107,14 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 01:07:07 PM</t>
@@ -6537,6 +7138,140 @@
       <c r="M40" s="3" t="inlineStr">
         <is>
           <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371906</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:37:15 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371906</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:37:15 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5071,10 +5071,8 @@
           <t>lalita magar</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9707987556</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9707987556</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5164,10 +5162,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5178,7 +5174,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5274,10 +5270,8 @@
           <t>lalita magar</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9707987556</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9707987556</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5367,10 +5361,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5381,7 +5373,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5477,10 +5469,8 @@
           <t>Ramita Pujari</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9818579073</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9818579073</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5515,10 +5505,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.711797</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.711797</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5566,48 +5554,147 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.304165</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.304165</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 5m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 5m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 5m</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 5m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="AA27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AC27" s="3" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr"/>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5633,7 +5720,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5661,7 +5748,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -5682,7 +5769,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7261,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -7241,7 +7328,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5700,6 +5700,315 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:29 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="AA29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="AA30" s="3" t="inlineStr"/>
+      <c r="AB30" s="3" t="inlineStr"/>
+      <c r="AC30" s="3" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5748,7 +6057,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -5769,7 +6078,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -518,7 +518,7 @@
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="36" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6009,6 +6009,1260 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371878</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9849270128</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849270128</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:10:07 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.7174</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Near By Kathmandu Fawlty Home P78W+X6R, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>swornimashrestha1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>09:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.295327</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371878</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9849270128</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9849270128</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:10:07 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.7174</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Near By Kathmandu Fawlty Home P78W+X6R, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>swornimashrestha1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>09:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.295327</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372114</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:13:06 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 06:56:12 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:21 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.689511</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>44600, Chandragiri 44600,Near Pokhrel Kirana Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>ganeshbarbot@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>06:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB575</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.24721</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>20h 42m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372114</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:13:06 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9841435071</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 06:56:12 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:21 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.689511</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>44600, Chandragiri 44600,Near Pokhrel Kirana Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>ganeshbarbot@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>06:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB575</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.24721</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>20h 42m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>iptv channel freeze issue</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372137</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>ram prashad phuyal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>ram prashad phuyal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9849149021</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:45 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>FNF9849149021</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:23:26 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:45 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>27.662973, 85.383567, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>06:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>20h 32m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371893</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:54:32 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:25:01 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:54:32 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.655215</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Gamcha chowk near, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>10:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>L46-2</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.393444</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 29m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6020,16 +7274,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6057,7 +7311,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -6067,7 +7321,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -6078,7 +7332,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -6090,7 +7344,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 23m</t>
+          <t>14h 30m</t>
         </is>
       </c>
     </row>
@@ -6102,7 +7356,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 25m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
@@ -6143,14 +7397,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -6161,10 +7415,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -6175,439 +7429,302 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1371454</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Roshan Joshi</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 09:46:24 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 10:14:03 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 27m</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1371642</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Raj shahi</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 11:50:55 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>15 Oct 2026 11:47:52 AM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>16 Oct 2026 12:02:10 PM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>1d 11m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 14m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1370690</t>
+          <t>TKT1371454</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Preju Khanal</t>
+          <t>Roshan Joshi</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -6637,54 +7754,54 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>14 Oct 2026 03:14:40 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>14 Oct 2026 03:14:40 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:12:32 PM</t>
+          <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 57m</t>
+          <t>1d 27m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 57m</t>
+          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1372115</t>
+          <t>TKT1371454</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sudip Danai</t>
+          <t>Roshan Joshi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -6704,44 +7821,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 07:10:35 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 07:00:54 PM</t>
+          <t>15 Oct 2026 09:46:24 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:27:38 PM</t>
+          <t>16 Oct 2026 10:14:03 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>17h 17m</t>
+          <t>1d 27m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>17h 26m</t>
+          <t>1d 27m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1372450</t>
+          <t>TKT1371642</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Rammani Devkota</t>
+          <t>Raj shahi</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6756,12 +7873,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -6771,44 +7888,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:48 AM</t>
+          <t>15 Oct 2026 11:50:55 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:02 AM</t>
+          <t>15 Oct 2026 11:47:52 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:41:11 PM</t>
+          <t>16 Oct 2026 12:02:10 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>3h 12m</t>
+          <t>1d 11m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>3h 13m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1372450</t>
+          <t>TKT1370690</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Rammani Devkota</t>
+          <t>Preju Khanal</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6838,54 +7955,54 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi-6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:48 AM</t>
+          <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:28:02 AM</t>
+          <t>14 Oct 2026 03:14:40 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 12:41:11 PM</t>
+          <t>16 Oct 2026 12:12:32 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3h 12m</t>
+          <t>1d 20h 57m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>3h 13m</t>
+          <t>1d 20h 57m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1372464</t>
+          <t>TKT1372115</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Abhaya Kc</t>
+          <t>Sudip Danai</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -6905,44 +8022,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : stb faulty   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>15 Oct 2026 07:10:35 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>15 Oct 2026 07:00:54 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:32:15 PM</t>
+          <t>16 Oct 2026 12:27:38 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>17h 17m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>17h 26m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1372464</t>
+          <t>TKT1372450</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Abhaya Kc</t>
+          <t>Rammani Devkota</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6972,44 +8089,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:48 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 09:38:30 AM</t>
+          <t>16 Oct 2026 09:28:02 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:32:15 PM</t>
+          <t>16 Oct 2026 12:41:11 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 12m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 13m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1371924</t>
+          <t>TKT1372450</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Pawan Pujari</t>
+          <t>Rammani Devkota</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7039,44 +8156,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6g router  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 03:48:18 PM</t>
+          <t>16 Oct 2026 09:28:48 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 03:48:18 PM</t>
+          <t>16 Oct 2026 09:28:02 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:33:51 PM</t>
+          <t>16 Oct 2026 12:41:11 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>21h 45m</t>
+          <t>3h 12m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>21h 45m</t>
+          <t>3h 13m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1372400</t>
+          <t>TKT1372464</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Samir Duwadi</t>
+          <t>Abhaya Kc</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -7106,44 +8223,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 08:45:59 AM</t>
+          <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 08:45:59 AM</t>
+          <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:08:36 PM</t>
+          <t>16 Oct 2026 01:32:15 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>5h 22m</t>
+          <t>3h 53m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>5h 22m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1372633</t>
+          <t>TKT1372464</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sea Design Pvt Ltd</t>
+          <t>Abhaya Kc</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7158,12 +8275,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -7173,44 +8290,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:09:02 PM</t>
+          <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 11:00:37 AM</t>
+          <t>16 Oct 2026 09:38:30 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:09:02 PM</t>
+          <t>16 Oct 2026 01:32:15 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 53m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>3h 8m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1372117</t>
+          <t>TKT1371924</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bibek shrestha</t>
+          <t>Pawan Pujari</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7225,12 +8342,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7240,44 +8357,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:08:26 PM</t>
+          <t>15 Oct 2026 03:48:18 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 07:02:29 PM</t>
+          <t>15 Oct 2026 03:48:18 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:08:26 PM</t>
+          <t>16 Oct 2026 01:33:51 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 45m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>19h 5m</t>
+          <t>21h 45m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1370063</t>
+          <t>TKT1372400</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Janak Adhikari</t>
+          <t>Samir Duwadi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7292,12 +8409,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7307,44 +8424,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:07:25 PM</t>
+          <t>16 Oct 2026 08:45:59 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>14 Oct 2026 10:04:07 AM</t>
+          <t>16 Oct 2026 08:45:59 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:07:25 PM</t>
+          <t>16 Oct 2026 02:08:36 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 22m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 4h 3m</t>
+          <t>5h 22m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1372009</t>
+          <t>TKT1372633</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bikash Kc</t>
+          <t>Sea Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7374,22 +8491,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:06:46 PM</t>
+          <t>16 Oct 2026 02:09:02 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 04:47:00 PM</t>
+          <t>16 Oct 2026 11:00:37 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:06:46 PM</t>
+          <t>16 Oct 2026 02:09:02 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7399,19 +8516,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>21h 19m</t>
+          <t>3h 8m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1371743</t>
+          <t>TKT1372117</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sanjeev Shahi</t>
+          <t>Bibek shrestha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7426,12 +8543,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7441,44 +8558,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 01:07:07 PM</t>
+          <t>16 Oct 2026 02:08:26 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 01:07:07 PM</t>
+          <t>15 Oct 2026 07:02:29 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:20:02 PM</t>
+          <t>16 Oct 2026 02:08:26 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>19h 5m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1371743</t>
+          <t>TKT1370063</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Shahi</t>
+          <t>Janak Adhikari</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7493,12 +8610,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -7508,44 +8625,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi-6 Router ugrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 01:07:07 PM</t>
+          <t>16 Oct 2026 02:07:25 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Oct 2026 01:07:07 PM</t>
+          <t>14 Oct 2026 10:04:07 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:20:02 PM</t>
+          <t>16 Oct 2026 02:07:25 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>2d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1371906</t>
+          <t>TKT1372009</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>lalita magar</t>
+          <t>Bikash Kc</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7560,12 +8677,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7575,99 +8692,702 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 03:32:03 PM</t>
+          <t>16 Oct 2026 02:06:46 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 03:32:03 PM</t>
+          <t>15 Oct 2026 04:47:00 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Oct 2026 02:37:15 PM</t>
+          <t>16 Oct 2026 02:06:46 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>23h 5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>23h 5m</t>
+          <t>21h 19m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371743</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sanjeev Shahi</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 01:07:07 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:20:02 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>TKT1371906</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>lalita magar</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 03:32:03 PM</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>15 Oct 2026 03:32:03 PM</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026 02:37:15 PM</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>23h 5m</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t>23h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371906</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>lalita magar</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:37:15 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371878</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:10:07 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371878</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Swornima Shrestha</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:10:14 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:10:07 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372114</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:13:06 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 06:56:12 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:21 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>20h 42m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1372114</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Gita Panthi</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:13:06 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 06:56:12 PM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:21 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>20h 42m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372137</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ram prashad phuyal</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:45 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 07:23:26 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:55:45 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>20h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371893</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:54:32 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 03:25:01 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:54:32 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>1d 29m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6076,10 +6076,8 @@
           <t>Swornima Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9849270128</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9849270128</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6114,10 +6112,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.7174</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.7174</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6173,25 +6169,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.295327</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.295327</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6287,10 +6279,8 @@
           <t>Swornima Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9849270128</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9849270128</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6325,10 +6315,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.7174</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.7174</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6384,25 +6372,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.295327</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.295327</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6498,10 +6482,8 @@
           <t>Gita Panthi</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841435071</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841435071</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6536,10 +6518,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.689511</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.689511</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6595,25 +6575,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB575</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.24721</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.24721</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6709,10 +6685,8 @@
           <t>Gita Panthi</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9841435071</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9841435071</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6747,10 +6721,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.689511</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.689511</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6806,25 +6778,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB575</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.24721</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.24721</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6920,10 +6888,8 @@
           <t>ram prashad phuyal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9849149021</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9849149021</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6991,10 +6957,8 @@
           <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -7013,10 +6977,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7027,7 +6989,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7123,10 +7085,8 @@
           <t>Pabitra khatri</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9865121028</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9865121028</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7161,10 +7121,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.655215</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.655215</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7216,25 +7174,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>L46-2</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.393444</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.393444</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7283,7 +7237,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9022,7 +8976,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -9089,7 +9043,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -9156,7 +9110,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -9223,7 +9177,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -9290,7 +9244,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv channel freeze issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -9357,7 +9311,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
